--- a/sample_data/sales.xlsx
+++ b/sample_data/sales.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Transactions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Regional_Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -6291,4 +6292,1830 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>order_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>order_date</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>gender</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>age</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>quantity</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>unit_price</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>discount</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>revenue</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>profit</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>customer_rating</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ORD-000583</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2023-01-01</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Haryana</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Clothing</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Fleece Hooded Sweatshirt</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>49</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>3089.71</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>3089.71</v>
+      </c>
+      <c r="M2" t="n">
+        <v>967.7</v>
+      </c>
+      <c r="N2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ORD-000057</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2023-01-02</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Gujarat</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Office Supplies</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Executive Rollerball Pen</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Non-Binary</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>49</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J3" t="n">
+        <v>879.1900000000001</v>
+      </c>
+      <c r="K3" t="n">
+        <v>10</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1582.54</v>
+      </c>
+      <c r="M3" t="n">
+        <v>305.09</v>
+      </c>
+      <c r="N3" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ORD-000378</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2023-01-02</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Karnataka</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ultra-wide Monitor</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>42</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>25891.55</v>
+      </c>
+      <c r="K4" t="n">
+        <v>15</v>
+      </c>
+      <c r="L4" t="n">
+        <v>22007.82</v>
+      </c>
+      <c r="M4" t="n">
+        <v>3841.15</v>
+      </c>
+      <c r="N4" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ORD-000593</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2023-01-02</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Office Supplies</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Magnetic Whiteboard</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>57</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3385.1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>15</v>
+      </c>
+      <c r="L5" t="n">
+        <v>5754.67</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1774.33</v>
+      </c>
+      <c r="N5" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ORD-000714</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2023-01-03</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Goa</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Furniture</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ergonomic Mesh Chair</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>48</v>
+      </c>
+      <c r="I6" t="n">
+        <v>8</v>
+      </c>
+      <c r="J6" t="n">
+        <v>13454.56</v>
+      </c>
+      <c r="K6" t="n">
+        <v>10</v>
+      </c>
+      <c r="L6" t="n">
+        <v>96872.83</v>
+      </c>
+      <c r="M6" t="n">
+        <v>28233.58</v>
+      </c>
+      <c r="N6" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ORD-000736</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2023-01-03</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Office Supplies</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Executive Rollerball Pen</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Non-Binary</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>37</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>851.97</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1703.94</v>
+      </c>
+      <c r="M7" t="n">
+        <v>447.64</v>
+      </c>
+      <c r="N7" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ORD-000779</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2023-01-03</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Delhi</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Ultra-wide Monitor</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Non-Binary</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>60</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J8" t="n">
+        <v>29024.96</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>87074.88</v>
+      </c>
+      <c r="M8" t="n">
+        <v>31459.58</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ORD-000005</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2023-01-04</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Kerala</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Office Supplies</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Heavy-Duty Binder</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>33</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>327.07</v>
+      </c>
+      <c r="K9" t="n">
+        <v>10</v>
+      </c>
+      <c r="L9" t="n">
+        <v>294.36</v>
+      </c>
+      <c r="M9" t="n">
+        <v>64.59</v>
+      </c>
+      <c r="N9" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ORD-000761</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2023-01-04</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Kerala</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Furniture</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Motorized Standing Desk</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>65</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2</v>
+      </c>
+      <c r="J10" t="n">
+        <v>25261.2</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>50522.4</v>
+      </c>
+      <c r="M10" t="n">
+        <v>12326.36</v>
+      </c>
+      <c r="N10" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ORD-000177</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2023-01-05</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Haryana</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Office Supplies</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Executive Rollerball Pen</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Non-Binary</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>25</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2</v>
+      </c>
+      <c r="J11" t="n">
+        <v>885.23</v>
+      </c>
+      <c r="K11" t="n">
+        <v>10</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1593.41</v>
+      </c>
+      <c r="M11" t="n">
+        <v>455.21</v>
+      </c>
+      <c r="N11" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ORD-000627</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2023-01-05</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Office Supplies</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Heavy-Duty Binder</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>39</v>
+      </c>
+      <c r="I12" t="n">
+        <v>5</v>
+      </c>
+      <c r="J12" t="n">
+        <v>365.5</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1827.5</v>
+      </c>
+      <c r="M12" t="n">
+        <v>688.14</v>
+      </c>
+      <c r="N12" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ORD-000844</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2023-01-05</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Assam</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Office Supplies</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Recycled Paper Ream</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>43</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" t="n">
+        <v>414.5</v>
+      </c>
+      <c r="K13" t="n">
+        <v>5</v>
+      </c>
+      <c r="L13" t="n">
+        <v>393.77</v>
+      </c>
+      <c r="M13" t="n">
+        <v>71.29000000000001</v>
+      </c>
+      <c r="N13" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ORD-000864</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2023-01-05</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Haryana</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Furniture</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Modular Bookshelf</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>45</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>8457.9</v>
+      </c>
+      <c r="K14" t="n">
+        <v>15</v>
+      </c>
+      <c r="L14" t="n">
+        <v>7189.22</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1199.46</v>
+      </c>
+      <c r="N14" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ORD-000454</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2023-01-06</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Punjab</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Furniture</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>LED Desk Lamp</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Non-Binary</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>19</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2165.81</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>2165.81</v>
+      </c>
+      <c r="M15" t="n">
+        <v>390.76</v>
+      </c>
+      <c r="N15" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ORD-000791</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2023-01-06</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Furniture</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Ergonomic Mesh Chair</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Non-Binary</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>18</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>12105.66</v>
+      </c>
+      <c r="K16" t="n">
+        <v>10</v>
+      </c>
+      <c r="L16" t="n">
+        <v>10895.09</v>
+      </c>
+      <c r="M16" t="n">
+        <v>3292.37</v>
+      </c>
+      <c r="N16" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ORD-000863</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2023-01-08</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Ultra-wide Monitor</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>59</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J17" t="n">
+        <v>29939.65</v>
+      </c>
+      <c r="K17" t="n">
+        <v>5</v>
+      </c>
+      <c r="L17" t="n">
+        <v>56885.33</v>
+      </c>
+      <c r="M17" t="n">
+        <v>14607.1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ORD-000514</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2023-01-09</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Delhi</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Office Supplies</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Executive Rollerball Pen</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>62</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>799.39</v>
+      </c>
+      <c r="K18" t="n">
+        <v>10</v>
+      </c>
+      <c r="L18" t="n">
+        <v>719.45</v>
+      </c>
+      <c r="M18" t="n">
+        <v>86.34</v>
+      </c>
+      <c r="N18" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ORD-000099</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2023-01-10</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Punjab</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Furniture</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Ergonomic Mesh Chair</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Non-Binary</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>64</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2</v>
+      </c>
+      <c r="J19" t="n">
+        <v>13069.34</v>
+      </c>
+      <c r="K19" t="n">
+        <v>10</v>
+      </c>
+      <c r="L19" t="n">
+        <v>23524.81</v>
+      </c>
+      <c r="M19" t="n">
+        <v>7746.99</v>
+      </c>
+      <c r="N19" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ORD-000571</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2023-01-11</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Office Supplies</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Magnetic Whiteboard</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>50</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3156.07</v>
+      </c>
+      <c r="K20" t="n">
+        <v>10</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2840.46</v>
+      </c>
+      <c r="M20" t="n">
+        <v>991.98</v>
+      </c>
+      <c r="N20" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ORD-000626</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2023-01-11</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Haryana</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Furniture</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Motorized Standing Desk</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Non-Binary</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>27</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" t="n">
+        <v>23444.43</v>
+      </c>
+      <c r="K21" t="n">
+        <v>10</v>
+      </c>
+      <c r="L21" t="n">
+        <v>21099.99</v>
+      </c>
+      <c r="M21" t="n">
+        <v>2875.23</v>
+      </c>
+      <c r="N21" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ORD-000657</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2023-01-11</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Delhi</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Clothing</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Fleece Hooded Sweatshirt</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>49</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3024.06</v>
+      </c>
+      <c r="K22" t="n">
+        <v>5</v>
+      </c>
+      <c r="L22" t="n">
+        <v>5745.71</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1876.35</v>
+      </c>
+      <c r="N22" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ORD-000852</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2023-01-12</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Karnataka</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Office Supplies</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Heavy-Duty Binder</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>33</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" t="n">
+        <v>368.84</v>
+      </c>
+      <c r="K23" t="n">
+        <v>5</v>
+      </c>
+      <c r="L23" t="n">
+        <v>350.4</v>
+      </c>
+      <c r="M23" t="n">
+        <v>43.36</v>
+      </c>
+      <c r="N23" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>ORD-000063</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2023-01-13</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Clothing</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Slim-fit Denim Jeans</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>41</v>
+      </c>
+      <c r="I24" t="n">
+        <v>6</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2999.02</v>
+      </c>
+      <c r="K24" t="n">
+        <v>15</v>
+      </c>
+      <c r="L24" t="n">
+        <v>15295</v>
+      </c>
+      <c r="M24" t="n">
+        <v>4366.19</v>
+      </c>
+      <c r="N24" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ORD-000066</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2023-01-13</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Kerala</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Office Supplies</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Heavy-Duty Binder</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>63</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" t="n">
+        <v>327.29</v>
+      </c>
+      <c r="K25" t="n">
+        <v>10</v>
+      </c>
+      <c r="L25" t="n">
+        <v>294.56</v>
+      </c>
+      <c r="M25" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="N25" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ORD-000536</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2023-01-13</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Wireless Earbuds</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>64</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" t="n">
+        <v>4847.08</v>
+      </c>
+      <c r="K26" t="n">
+        <v>10</v>
+      </c>
+      <c r="L26" t="n">
+        <v>4362.37</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1355.42</v>
+      </c>
+      <c r="N26" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ORD-000104</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2023-01-14</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Goa</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Clothing</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Slim-fit Denim Jeans</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>64</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2633.36</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>2633.36</v>
+      </c>
+      <c r="M27" t="n">
+        <v>411.05</v>
+      </c>
+      <c r="N27" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ORD-000303</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2023-01-14</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Rajasthan</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Clothing</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Breathable Running Shoes</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>36</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" t="n">
+        <v>4292.46</v>
+      </c>
+      <c r="K28" t="n">
+        <v>5</v>
+      </c>
+      <c r="L28" t="n">
+        <v>4077.84</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1289.03</v>
+      </c>
+      <c r="N28" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>ORD-000150</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2023-01-15</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Office Supplies</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Magnetic Whiteboard</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>49</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1</v>
+      </c>
+      <c r="J29" t="n">
+        <v>3327.98</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>3327.98</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1176.42</v>
+      </c>
+      <c r="N29" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>ORD-000268</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2023-01-15</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Office Supplies</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Executive Rollerball Pen</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>64</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" t="n">
+        <v>911.83</v>
+      </c>
+      <c r="K30" t="n">
+        <v>10</v>
+      </c>
+      <c r="L30" t="n">
+        <v>820.65</v>
+      </c>
+      <c r="M30" t="n">
+        <v>179.57</v>
+      </c>
+      <c r="N30" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>ORD-000624</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2023-01-15</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Furniture</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>LED Desk Lamp</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>49</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2075.84</v>
+      </c>
+      <c r="K31" t="n">
+        <v>25</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1556.88</v>
+      </c>
+      <c r="M31" t="n">
+        <v>494.18</v>
+      </c>
+      <c r="N31" t="n">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/sample_data/sales.xlsx
+++ b/sample_data/sales.xlsx
@@ -492,12 +492,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ORD-000583</t>
+          <t>ORD-000001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2023-01-01</t>
+          <t>2022-08-17</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -507,17 +507,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Haryana</t>
+          <t>Punjab</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Furniture</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fleece Hooded Sweatshirt</t>
+          <t>Motorized Standing Desk</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -526,94 +526,94 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J2" t="n">
-        <v>3089.71</v>
+        <v>22784.39</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L2" t="n">
-        <v>3089.71</v>
+        <v>61517.85</v>
       </c>
       <c r="M2" t="n">
-        <v>967.7</v>
+        <v>16928.55</v>
       </c>
       <c r="N2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ORD-000057</t>
+          <t>ORD-000002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2023-01-02</t>
+          <t>2022-07-29</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>North</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Gujarat</t>
+          <t>Haryana</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Office Supplies</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Executive Rollerball Pen</t>
+          <t>Laptop Pro</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Non-Binary</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>879.1900000000001</v>
+        <v>68808.23</v>
       </c>
       <c r="K3" t="n">
         <v>10</v>
       </c>
       <c r="L3" t="n">
-        <v>1582.54</v>
+        <v>61927.41</v>
       </c>
       <c r="M3" t="n">
-        <v>305.09</v>
+        <v>18832.06</v>
       </c>
       <c r="N3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ORD-000378</t>
+          <t>ORD-000003</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2023-01-02</t>
+          <t>2023-03-24</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -628,12 +628,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Furniture</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ultra-wide Monitor</t>
+          <t>LED Desk Lamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -642,22 +642,22 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J4" t="n">
-        <v>25891.55</v>
+        <v>2354.37</v>
       </c>
       <c r="K4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>22007.82</v>
+        <v>7063.11</v>
       </c>
       <c r="M4" t="n">
-        <v>3841.15</v>
+        <v>2669.68</v>
       </c>
       <c r="N4" t="n">
         <v>4</v>
@@ -666,12 +666,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ORD-000593</t>
+          <t>ORD-000004</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2023-01-02</t>
+          <t>2023-03-28</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -681,55 +681,55 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>West Bengal</t>
+          <t>Odisha</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Office Supplies</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Magnetic Whiteboard</t>
+          <t>Smartphone 5G</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Non-Binary</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>29558.08</v>
+      </c>
+      <c r="K5" t="n">
+        <v>5</v>
+      </c>
+      <c r="L5" t="n">
+        <v>28080.18</v>
+      </c>
+      <c r="M5" t="n">
+        <v>6288.95</v>
+      </c>
+      <c r="N5" t="n">
         <v>2</v>
-      </c>
-      <c r="J5" t="n">
-        <v>3385.1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>15</v>
-      </c>
-      <c r="L5" t="n">
-        <v>5754.67</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1774.33</v>
-      </c>
-      <c r="N5" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ORD-000714</t>
+          <t>ORD-000005</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2023-01-03</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Rajasthan</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -749,103 +749,103 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ergonomic Mesh Chair</t>
+          <t>Motorized Standing Desk</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="I6" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>13454.56</v>
+        <v>22427.93</v>
       </c>
       <c r="K6" t="n">
         <v>10</v>
       </c>
       <c r="L6" t="n">
-        <v>96872.83</v>
+        <v>20185.14</v>
       </c>
       <c r="M6" t="n">
-        <v>28233.58</v>
+        <v>4429.43</v>
       </c>
       <c r="N6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ORD-000736</t>
+          <t>ORD-000006</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2023-01-03</t>
+          <t>2022-07-29</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>North</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>West Bengal</t>
+          <t>Haryana</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Office Supplies</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Executive Rollerball Pen</t>
+          <t>Wireless Earbuds</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Non-Binary</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J7" t="n">
-        <v>851.97</v>
+        <v>4629.82</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L7" t="n">
-        <v>1703.94</v>
+        <v>17593.32</v>
       </c>
       <c r="M7" t="n">
-        <v>447.64</v>
+        <v>2171.88</v>
       </c>
       <c r="N7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ORD-000779</t>
+          <t>ORD-000007</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2023-01-03</t>
+          <t>2023-06-26</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Haryana</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -870,108 +870,108 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Non-Binary</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J8" t="n">
-        <v>29024.96</v>
+        <v>27124.67</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>87074.88</v>
+        <v>108498.68</v>
       </c>
       <c r="M8" t="n">
-        <v>31459.58</v>
+        <v>32321.82</v>
       </c>
       <c r="N8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ORD-000005</t>
+          <t>ORD-000008</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2023-01-04</t>
+          <t>2023-08-24</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>West</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Gujarat</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Office Supplies</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Heavy-Duty Binder</t>
+          <t>Laptop Pro</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Non-Binary</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J9" t="n">
-        <v>327.07</v>
+        <v>68465.23</v>
       </c>
       <c r="K9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>294.36</v>
+        <v>136930.46</v>
       </c>
       <c r="M9" t="n">
-        <v>64.59</v>
+        <v>30354.16</v>
       </c>
       <c r="N9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ORD-000761</t>
+          <t>ORD-000009</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2023-01-04</t>
+          <t>2023-04-12</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>West</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -981,147 +981,147 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Motorized Standing Desk</t>
+          <t>Ergonomic Mesh Chair</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>65</v>
+        <v>21</v>
       </c>
       <c r="I10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>25261.2</v>
+        <v>12540.14</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L10" t="n">
-        <v>50522.4</v>
+        <v>11913.13</v>
       </c>
       <c r="M10" t="n">
-        <v>12326.36</v>
+        <v>2002.15</v>
       </c>
       <c r="N10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ORD-000177</t>
+          <t>ORD-000010</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2023-01-05</t>
+          <t>2023-07-24</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>East</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Haryana</t>
+          <t>Odisha</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Office Supplies</t>
+          <t>Furniture</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Executive Rollerball Pen</t>
+          <t>Modular Bookshelf</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Non-Binary</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="I11" t="n">
         <v>2</v>
       </c>
       <c r="J11" t="n">
-        <v>885.23</v>
+        <v>8357.4</v>
       </c>
       <c r="K11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L11" t="n">
-        <v>1593.41</v>
+        <v>13371.84</v>
       </c>
       <c r="M11" t="n">
-        <v>455.21</v>
+        <v>4133.11</v>
       </c>
       <c r="N11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ORD-000627</t>
+          <t>ORD-000011</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2023-01-05</t>
+          <t>2023-03-06</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>West</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Telangana</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Office Supplies</t>
+          <t>Furniture</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Heavy-Duty Binder</t>
+          <t>LED Desk Lamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Non-Binary</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="I12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>365.5</v>
+        <v>2039.92</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1827.5</v>
+        <v>2039.92</v>
       </c>
       <c r="M12" t="n">
-        <v>688.14</v>
+        <v>450.94</v>
       </c>
       <c r="N12" t="n">
         <v>3</v>
@@ -1130,56 +1130,56 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ORD-000844</t>
+          <t>ORD-000012</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2023-01-05</t>
+          <t>2023-05-17</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>South</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Assam</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Office Supplies</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Recycled Paper Ream</t>
+          <t>Wrinkle-Free Formal Shirt</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Non-Binary</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>414.5</v>
+        <v>2122.89</v>
       </c>
       <c r="K13" t="n">
         <v>5</v>
       </c>
       <c r="L13" t="n">
-        <v>393.77</v>
+        <v>2016.75</v>
       </c>
       <c r="M13" t="n">
-        <v>71.29000000000001</v>
+        <v>315.9</v>
       </c>
       <c r="N13" t="n">
         <v>5</v>
@@ -1188,22 +1188,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ORD-000864</t>
+          <t>ORD-000013</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2023-01-05</t>
+          <t>2023-03-26</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>West</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Haryana</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1213,55 +1213,55 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Modular Bookshelf</t>
+          <t>Ergonomic Mesh Chair</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>8457.9</v>
+        <v>12346.8</v>
       </c>
       <c r="K14" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="L14" t="n">
-        <v>7189.22</v>
+        <v>11729.46</v>
       </c>
       <c r="M14" t="n">
-        <v>1199.46</v>
+        <v>2302.57</v>
       </c>
       <c r="N14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ORD-000454</t>
+          <t>ORD-000014</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2023-01-06</t>
+          <t>2024-04-01</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>West</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Punjab</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1280,22 +1280,22 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J15" t="n">
-        <v>2165.81</v>
+        <v>2302.14</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L15" t="n">
-        <v>2165.81</v>
+        <v>6215.78</v>
       </c>
       <c r="M15" t="n">
-        <v>390.76</v>
+        <v>2242.89</v>
       </c>
       <c r="N15" t="n">
         <v>4</v>
@@ -1304,12 +1304,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ORD-000791</t>
+          <t>ORD-000015</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2023-01-06</t>
+          <t>2023-10-07</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1319,41 +1319,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Telangana</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Furniture</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ergonomic Mesh Chair</t>
+          <t>Fleece Hooded Sweatshirt</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Non-Binary</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J16" t="n">
-        <v>12105.66</v>
+        <v>3161.16</v>
       </c>
       <c r="K16" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>10895.09</v>
+        <v>12644.64</v>
       </c>
       <c r="M16" t="n">
-        <v>3292.37</v>
+        <v>1726.31</v>
       </c>
       <c r="N16" t="n">
         <v>4</v>
@@ -1362,12 +1362,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ORD-000863</t>
+          <t>ORD-000016</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2023-01-08</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1377,99 +1377,99 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Telangana</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Office Supplies</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ultra-wide Monitor</t>
+          <t>Magnetic Whiteboard</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J17" t="n">
-        <v>29939.65</v>
+        <v>3246.74</v>
       </c>
       <c r="K17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>56885.33</v>
+        <v>9740.219999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>14607.1</v>
+        <v>2590.15</v>
       </c>
       <c r="N17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ORD-000514</t>
+          <t>ORD-000017</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2023-01-09</t>
+          <t>2024-03-28</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>West</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Gujarat</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Office Supplies</t>
+          <t>Furniture</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Executive Rollerball Pen</t>
+          <t>LED Desk Lamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J18" t="n">
-        <v>799.39</v>
+        <v>2291.8</v>
       </c>
       <c r="K18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L18" t="n">
-        <v>719.45</v>
+        <v>6531.63</v>
       </c>
       <c r="M18" t="n">
-        <v>86.34</v>
+        <v>2093.07</v>
       </c>
       <c r="N18" t="n">
         <v>4</v>
@@ -1478,12 +1478,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ORD-000099</t>
+          <t>ORD-000018</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2023-01-10</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Punjab</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ergonomic Mesh Chair</t>
+          <t>Motorized Standing Desk</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1512,22 +1512,22 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>64</v>
+        <v>26</v>
       </c>
       <c r="I19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J19" t="n">
-        <v>13069.34</v>
+        <v>22505.82</v>
       </c>
       <c r="K19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L19" t="n">
-        <v>23524.81</v>
+        <v>64141.59</v>
       </c>
       <c r="M19" t="n">
-        <v>7746.99</v>
+        <v>11061.02</v>
       </c>
       <c r="N19" t="n">
         <v>5</v>
@@ -1536,128 +1536,128 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ORD-000571</t>
+          <t>ORD-000019</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2023-01-11</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>North</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>West Bengal</t>
+          <t>Haryana</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Office Supplies</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Magnetic Whiteboard</t>
+          <t>Breathable Running Shoes</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="I20" t="n">
         <v>1</v>
       </c>
       <c r="J20" t="n">
-        <v>3156.07</v>
+        <v>4506.17</v>
       </c>
       <c r="K20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L20" t="n">
-        <v>2840.46</v>
+        <v>3604.94</v>
       </c>
       <c r="M20" t="n">
-        <v>991.98</v>
+        <v>666.25</v>
       </c>
       <c r="N20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ORD-000626</t>
+          <t>ORD-000020</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2023-01-11</t>
+          <t>2024-12-19</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>West</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Haryana</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Furniture</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Motorized Standing Desk</t>
+          <t>Smart Fitness Watch</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Non-Binary</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="I21" t="n">
         <v>1</v>
       </c>
       <c r="J21" t="n">
-        <v>23444.43</v>
+        <v>6425.14</v>
       </c>
       <c r="K21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L21" t="n">
-        <v>21099.99</v>
+        <v>6103.88</v>
       </c>
       <c r="M21" t="n">
-        <v>2875.23</v>
+        <v>1835.1</v>
       </c>
       <c r="N21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ORD-000657</t>
+          <t>ORD-000021</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2023-01-11</t>
+          <t>2023-11-28</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Punjab</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fleece Hooded Sweatshirt</t>
+          <t>Slim-fit Denim Jeans</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1686,22 +1686,22 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="I22" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J22" t="n">
-        <v>3024.06</v>
+        <v>2859.76</v>
       </c>
       <c r="K22" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="L22" t="n">
-        <v>5745.71</v>
+        <v>9723.18</v>
       </c>
       <c r="M22" t="n">
-        <v>1876.35</v>
+        <v>3198.49</v>
       </c>
       <c r="N22" t="n">
         <v>3</v>
@@ -1710,56 +1710,56 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ORD-000852</t>
+          <t>ORD-000022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2023-01-12</t>
+          <t>2022-01-07</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>West</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>Gujarat</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Office Supplies</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Heavy-Duty Binder</t>
+          <t>Wireless Earbuds</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Non-Binary</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J23" t="n">
-        <v>368.84</v>
+        <v>4373.53</v>
       </c>
       <c r="K23" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>350.4</v>
+        <v>21867.65</v>
       </c>
       <c r="M23" t="n">
-        <v>43.36</v>
+        <v>4649.88</v>
       </c>
       <c r="N23" t="n">
         <v>5</v>
@@ -1768,12 +1768,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ORD-000063</t>
+          <t>ORD-000023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2023-01-13</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1783,75 +1783,75 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Telangana</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Office Supplies</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Slim-fit Denim Jeans</t>
+          <t>Executive Rollerball Pen</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Non-Binary</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="I24" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
-        <v>2999.02</v>
+        <v>840.09</v>
       </c>
       <c r="K24" t="n">
         <v>15</v>
       </c>
       <c r="L24" t="n">
-        <v>15295</v>
+        <v>714.08</v>
       </c>
       <c r="M24" t="n">
-        <v>4366.19</v>
+        <v>245.49</v>
       </c>
       <c r="N24" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ORD-000066</t>
+          <t>ORD-000024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2023-01-13</t>
+          <t>2024-12-22</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>North</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Punjab</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Office Supplies</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Heavy-Duty Binder</t>
+          <t>Premium Cotton T-Shirt</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1860,46 +1860,46 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J25" t="n">
-        <v>327.29</v>
+        <v>1197.09</v>
       </c>
       <c r="K25" t="n">
         <v>10</v>
       </c>
       <c r="L25" t="n">
-        <v>294.56</v>
+        <v>2154.76</v>
       </c>
       <c r="M25" t="n">
-        <v>40.8</v>
+        <v>409.51</v>
       </c>
       <c r="N25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ORD-000536</t>
+          <t>ORD-000025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2023-01-13</t>
+          <t>2024-01-14</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>West</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Telangana</t>
+          <t>Gujarat</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1909,65 +1909,65 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Wireless Earbuds</t>
+          <t>Smartphone 5G</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Non-Binary</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J26" t="n">
-        <v>4847.08</v>
+        <v>33039.46</v>
       </c>
       <c r="K26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L26" t="n">
-        <v>4362.37</v>
+        <v>62774.97</v>
       </c>
       <c r="M26" t="n">
-        <v>1355.42</v>
+        <v>23393.93</v>
       </c>
       <c r="N26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ORD-000104</t>
+          <t>ORD-000026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2023-01-14</t>
+          <t>2022-06-11</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>North</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Haryana</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Slim-fit Denim Jeans</t>
+          <t>Smart Fitness Watch</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1976,22 +1976,22 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J27" t="n">
-        <v>2633.36</v>
+        <v>5808.84</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>2633.36</v>
+        <v>11617.68</v>
       </c>
       <c r="M27" t="n">
-        <v>411.05</v>
+        <v>1505.54</v>
       </c>
       <c r="N27" t="n">
         <v>4</v>
@@ -2000,56 +2000,56 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ORD-000303</t>
+          <t>ORD-000027</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2023-01-14</t>
+          <t>2022-09-20</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>East</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Rajasthan</t>
+          <t>Bihar</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Office Supplies</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Breathable Running Shoes</t>
+          <t>Magnetic Whiteboard</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Non-Binary</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J28" t="n">
-        <v>4292.46</v>
+        <v>2960.92</v>
       </c>
       <c r="K28" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>4077.84</v>
+        <v>5921.84</v>
       </c>
       <c r="M28" t="n">
-        <v>1289.03</v>
+        <v>1687.32</v>
       </c>
       <c r="N28" t="n">
         <v>4</v>
@@ -2058,12 +2058,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ORD-000150</t>
+          <t>ORD-000028</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2023-01-15</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2083,65 +2083,65 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Magnetic Whiteboard</t>
+          <t>Steel Stapler Set</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Non-Binary</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J29" t="n">
-        <v>3327.98</v>
+        <v>605.08</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L29" t="n">
-        <v>3327.98</v>
+        <v>1149.65</v>
       </c>
       <c r="M29" t="n">
-        <v>1176.42</v>
+        <v>162.13</v>
       </c>
       <c r="N29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ORD-000268</t>
+          <t>ORD-000029</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2023-01-15</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>East</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Assam</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Office Supplies</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Executive Rollerball Pen</t>
+          <t>Smartphone 5G</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2150,46 +2150,46 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>64</v>
+        <v>34</v>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J30" t="n">
-        <v>911.83</v>
+        <v>31323.05</v>
       </c>
       <c r="K30" t="n">
         <v>10</v>
       </c>
       <c r="L30" t="n">
-        <v>820.65</v>
+        <v>84572.24000000001</v>
       </c>
       <c r="M30" t="n">
-        <v>179.57</v>
+        <v>24079.22</v>
       </c>
       <c r="N30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ORD-000624</t>
+          <t>ORD-000030</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2023-01-15</t>
+          <t>2022-05-12</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>West</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>West Bengal</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2208,22 +2208,22 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J31" t="n">
-        <v>2075.84</v>
+        <v>2077.05</v>
       </c>
       <c r="K31" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="L31" t="n">
-        <v>1556.88</v>
+        <v>5919.59</v>
       </c>
       <c r="M31" t="n">
-        <v>494.18</v>
+        <v>1781.27</v>
       </c>
       <c r="N31" t="n">
         <v>5</v>
@@ -2232,56 +2232,56 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ORD-000676</t>
+          <t>ORD-000031</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2023-01-15</t>
+          <t>2022-01-15</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>North</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Furniture</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Premium Cotton T-Shirt</t>
+          <t>Ergonomic Mesh Chair</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I32" t="n">
         <v>1</v>
       </c>
       <c r="J32" t="n">
-        <v>1173.61</v>
+        <v>12524.19</v>
       </c>
       <c r="K32" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>997.5700000000001</v>
+        <v>12524.19</v>
       </c>
       <c r="M32" t="n">
-        <v>204.83</v>
+        <v>3603.77</v>
       </c>
       <c r="N32" t="n">
         <v>3</v>
@@ -2290,22 +2290,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ORD-000801</t>
+          <t>ORD-000032</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2023-01-15</t>
+          <t>2023-11-08</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>North</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>West Bengal</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2315,45 +2315,45 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Recycled Paper Ream</t>
+          <t>Steel Stapler Set</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I33" t="n">
         <v>1</v>
       </c>
       <c r="J33" t="n">
-        <v>433.35</v>
+        <v>601.7</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L33" t="n">
-        <v>433.35</v>
+        <v>511.44</v>
       </c>
       <c r="M33" t="n">
-        <v>79.81999999999999</v>
+        <v>151.22</v>
       </c>
       <c r="N33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ORD-000314</t>
+          <t>ORD-000033</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2023-01-16</t>
+          <t>2022-09-28</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2363,17 +2363,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Odisha</t>
+          <t>Bihar</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Office Supplies</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Steel Stapler Set</t>
+          <t>Fleece Hooded Sweatshirt</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2382,56 +2382,56 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="I34" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J34" t="n">
-        <v>642.51</v>
+        <v>3287.16</v>
       </c>
       <c r="K34" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>1638.4</v>
+        <v>16435.8</v>
       </c>
       <c r="M34" t="n">
-        <v>229.16</v>
+        <v>4792.61</v>
       </c>
       <c r="N34" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ORD-000932</t>
+          <t>ORD-000034</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2023-01-16</t>
+          <t>2022-07-13</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>North</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Haryana</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Office Supplies</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Wrinkle-Free Formal Shirt</t>
+          <t>Steel Stapler Set</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2440,56 +2440,56 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="I35" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" t="n">
+        <v>560.9400000000001</v>
+      </c>
+      <c r="K35" t="n">
+        <v>15</v>
+      </c>
+      <c r="L35" t="n">
+        <v>476.8</v>
+      </c>
+      <c r="M35" t="n">
+        <v>168.84</v>
+      </c>
+      <c r="N35" t="n">
         <v>4</v>
-      </c>
-      <c r="J35" t="n">
-        <v>2133.61</v>
-      </c>
-      <c r="K35" t="n">
-        <v>5</v>
-      </c>
-      <c r="L35" t="n">
-        <v>8107.72</v>
-      </c>
-      <c r="M35" t="n">
-        <v>2032.73</v>
-      </c>
-      <c r="N35" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ORD-000982</t>
+          <t>ORD-000035</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2023-01-16</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>North</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Furniture</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>LED Desk Lamp</t>
+          <t>Ultra-wide Monitor</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2498,22 +2498,22 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="I36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
-        <v>2135.14</v>
+        <v>28897.6</v>
       </c>
       <c r="K36" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="L36" t="n">
-        <v>3843.25</v>
+        <v>24562.96</v>
       </c>
       <c r="M36" t="n">
-        <v>680.89</v>
+        <v>8416.360000000001</v>
       </c>
       <c r="N36" t="n">
         <v>4</v>
@@ -2522,56 +2522,56 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ORD-000482</t>
+          <t>ORD-000036</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2023-01-17</t>
+          <t>2023-11-26</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>North</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Odisha</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Office Supplies</t>
+          <t>Furniture</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Recycled Paper Ream</t>
+          <t>Motorized Standing Desk</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Non-Binary</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="I37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J37" t="n">
-        <v>470.19</v>
+        <v>22403.1</v>
       </c>
       <c r="K37" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>1340.04</v>
+        <v>44806.2</v>
       </c>
       <c r="M37" t="n">
-        <v>299.47</v>
+        <v>15844.55</v>
       </c>
       <c r="N37" t="n">
         <v>4</v>
@@ -2580,56 +2580,56 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ORD-000706</t>
+          <t>ORD-000037</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2023-01-17</t>
+          <t>2024-07-07</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>South</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Furniture</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Smart Fitness Watch</t>
+          <t>Modular Bookshelf</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Non-Binary</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="I38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J38" t="n">
-        <v>5795.83</v>
+        <v>9098.58</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="L38" t="n">
-        <v>11591.66</v>
+        <v>6823.94</v>
       </c>
       <c r="M38" t="n">
-        <v>2391.59</v>
+        <v>1322.61</v>
       </c>
       <c r="N38" t="n">
         <v>4</v>
@@ -2638,22 +2638,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ORD-000984</t>
+          <t>ORD-000038</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2023-01-17</t>
+          <t>2023-05-27</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>North</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Haryana</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2663,31 +2663,31 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ultra-wide Monitor</t>
+          <t>Laptop Pro</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Non-Binary</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="I39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J39" t="n">
-        <v>28323.33</v>
+        <v>66580.39999999999</v>
       </c>
       <c r="K39" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>45317.33</v>
+        <v>199741.2</v>
       </c>
       <c r="M39" t="n">
-        <v>15549.91</v>
+        <v>60954.34</v>
       </c>
       <c r="N39" t="n">
         <v>3</v>
@@ -2696,172 +2696,172 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ORD-000586</t>
+          <t>ORD-000039</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2023-01-18</t>
+          <t>2022-01-31</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>North</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Office Supplies</t>
+          <t>Furniture</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Heavy-Duty Binder</t>
+          <t>Executive Leather Sofa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="I40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J40" t="n">
-        <v>362.47</v>
+        <v>34252.23</v>
       </c>
       <c r="K40" t="n">
         <v>10</v>
       </c>
       <c r="L40" t="n">
-        <v>652.45</v>
+        <v>30827.01</v>
       </c>
       <c r="M40" t="n">
-        <v>198.53</v>
+        <v>9477.59</v>
       </c>
       <c r="N40" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ORD-000891</t>
+          <t>ORD-000040</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2023-01-18</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>South</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Furniture</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Modular Bookshelf</t>
+          <t>Smartphone 5G</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="I41" t="n">
         <v>1</v>
       </c>
       <c r="J41" t="n">
-        <v>8544.16</v>
+        <v>31322.7</v>
       </c>
       <c r="K41" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>8116.95</v>
+        <v>31322.7</v>
       </c>
       <c r="M41" t="n">
-        <v>2241.51</v>
+        <v>5745.75</v>
       </c>
       <c r="N41" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ORD-000161</t>
+          <t>ORD-000041</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2023-01-19</t>
+          <t>2022-01-05</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>East</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Telangana</t>
+          <t>Odisha</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ultra-wide Monitor</t>
+          <t>Wrinkle-Free Formal Shirt</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="I42" t="n">
         <v>2</v>
       </c>
       <c r="J42" t="n">
-        <v>27594.16</v>
+        <v>2342.95</v>
       </c>
       <c r="K42" t="n">
         <v>5</v>
       </c>
       <c r="L42" t="n">
-        <v>52428.9</v>
+        <v>4451.61</v>
       </c>
       <c r="M42" t="n">
-        <v>12236.53</v>
+        <v>939.38</v>
       </c>
       <c r="N42" t="n">
         <v>4</v>
@@ -2870,22 +2870,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ORD-000529</t>
+          <t>ORD-000042</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2023-01-19</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>South</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Bihar</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2900,84 +2900,84 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="I43" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J43" t="n">
-        <v>789.03</v>
+        <v>808.55</v>
       </c>
       <c r="K43" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L43" t="n">
-        <v>4497.47</v>
+        <v>1455.39</v>
       </c>
       <c r="M43" t="n">
-        <v>1379.81</v>
+        <v>280.89</v>
       </c>
       <c r="N43" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ORD-000635</t>
+          <t>ORD-000043</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2023-01-19</t>
+          <t>2022-05-05</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>West</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Telangana</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Furniture</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>LED Desk Lamp</t>
+          <t>Smart Fitness Watch</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Non-Binary</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="I44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J44" t="n">
-        <v>2292.38</v>
+        <v>6474.77</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L44" t="n">
-        <v>4584.76</v>
+        <v>6151.03</v>
       </c>
       <c r="M44" t="n">
-        <v>784.3099999999999</v>
+        <v>1185.22</v>
       </c>
       <c r="N44" t="n">
         <v>5</v>
@@ -2986,114 +2986,114 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ORD-000686</t>
+          <t>ORD-000044</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2023-01-19</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>South</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Office Supplies</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Magnetic Whiteboard</t>
+          <t>Smartphone 5G</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Non-Binary</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J45" t="n">
-        <v>3394.22</v>
+        <v>31133.44</v>
       </c>
       <c r="K45" t="n">
         <v>5</v>
       </c>
       <c r="L45" t="n">
-        <v>3224.51</v>
+        <v>177460.61</v>
       </c>
       <c r="M45" t="n">
-        <v>580.92</v>
+        <v>47700.71</v>
       </c>
       <c r="N45" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ORD-000269</t>
+          <t>ORD-000045</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2023-01-20</t>
+          <t>2022-05-20</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>South</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Furniture</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Executive Leather Sofa</t>
+          <t>Smart Fitness Watch</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="I46" t="n">
         <v>1</v>
       </c>
       <c r="J46" t="n">
-        <v>32767.96</v>
+        <v>5777.74</v>
       </c>
       <c r="K46" t="n">
         <v>5</v>
       </c>
       <c r="L46" t="n">
-        <v>31129.56</v>
+        <v>5488.85</v>
       </c>
       <c r="M46" t="n">
-        <v>5813.82</v>
+        <v>1190.52</v>
       </c>
       <c r="N46" t="n">
         <v>4</v>
@@ -3102,172 +3102,172 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ORD-000357</t>
+          <t>ORD-000046</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2023-01-20</t>
+          <t>2022-03-23</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>North</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Haryana</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Furniture</t>
+          <t>Office Supplies</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ergonomic Mesh Chair</t>
+          <t>Heavy-Duty Binder</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>67</v>
+        <v>20</v>
       </c>
       <c r="I47" t="n">
         <v>2</v>
       </c>
       <c r="J47" t="n">
-        <v>12194.69</v>
+        <v>327.44</v>
       </c>
       <c r="K47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="L47" t="n">
-        <v>20730.97</v>
+        <v>589.39</v>
       </c>
       <c r="M47" t="n">
-        <v>2605.35</v>
+        <v>222.44</v>
       </c>
       <c r="N47" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ORD-000570</t>
+          <t>ORD-000047</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2023-01-20</t>
+          <t>2023-10-06</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>South</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Telangana</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Furniture</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>LED Desk Lamp</t>
+          <t>Slim-fit Denim Jeans</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Non-Binary</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="I48" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J48" t="n">
-        <v>2327.77</v>
+        <v>2720.5</v>
       </c>
       <c r="K48" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="L48" t="n">
-        <v>6634.14</v>
+        <v>2312.43</v>
       </c>
       <c r="M48" t="n">
-        <v>2157.77</v>
+        <v>359.63</v>
       </c>
       <c r="N48" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ORD-000100</t>
+          <t>ORD-000048</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2023-01-21</t>
+          <t>2023-09-07</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>East</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Uttar Pradesh</t>
+          <t>Odisha</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Furniture</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ergonomic Mesh Chair</t>
+          <t>Laptop Pro</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Non-Binary</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="I49" t="n">
         <v>1</v>
       </c>
       <c r="J49" t="n">
-        <v>12679.84</v>
+        <v>68217.36</v>
       </c>
       <c r="K49" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="L49" t="n">
-        <v>12045.85</v>
+        <v>57984.76</v>
       </c>
       <c r="M49" t="n">
-        <v>2815.64</v>
+        <v>20030.19</v>
       </c>
       <c r="N49" t="n">
         <v>5</v>
@@ -3276,12 +3276,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ORD-000399</t>
+          <t>ORD-000049</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2023-01-21</t>
+          <t>2022-07-24</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3296,60 +3296,60 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Furniture</t>
+          <t>Office Supplies</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Executive Leather Sofa</t>
+          <t>Executive Rollerball Pen</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J50" t="n">
-        <v>36844.01</v>
+        <v>890.5700000000001</v>
       </c>
       <c r="K50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="L50" t="n">
-        <v>93952.23</v>
+        <v>1603.03</v>
       </c>
       <c r="M50" t="n">
-        <v>25241.28</v>
+        <v>484.93</v>
       </c>
       <c r="N50" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ORD-000668</t>
+          <t>ORD-000050</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2023-01-21</t>
+          <t>2022-05-21</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>South</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Rajasthan</t>
+          <t>Telangana</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3359,31 +3359,31 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Steel Stapler Set</t>
+          <t>Executive Rollerball Pen</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Non-Binary</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>64</v>
+        <v>29</v>
       </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J51" t="n">
-        <v>607.8200000000001</v>
+        <v>785.76</v>
       </c>
       <c r="K51" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L51" t="n">
-        <v>607.8200000000001</v>
+        <v>3732.36</v>
       </c>
       <c r="M51" t="n">
-        <v>210.9</v>
+        <v>873.38</v>
       </c>
       <c r="N51" t="n">
         <v>4</v>
@@ -3392,22 +3392,22 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ORD-000060</t>
+          <t>ORD-000051</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2023-01-22</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>North</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Rajasthan</t>
+          <t>Punjab</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3417,31 +3417,31 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Wireless Earbuds</t>
+          <t>Smartphone 5G</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="I52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J52" t="n">
-        <v>4210.44</v>
+        <v>34467.03</v>
       </c>
       <c r="K52" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="L52" t="n">
-        <v>7999.84</v>
+        <v>29296.98</v>
       </c>
       <c r="M52" t="n">
-        <v>1944.78</v>
+        <v>10069.52</v>
       </c>
       <c r="N52" t="n">
         <v>3</v>
@@ -3450,56 +3450,56 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ORD-000231</t>
+          <t>ORD-000052</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2023-01-22</t>
+          <t>2022-08-25</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>North</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>West Bengal</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Office Supplies</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Premium Cotton T-Shirt</t>
+          <t>Heavy-Duty Binder</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Non-Binary</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="I53" t="n">
         <v>4</v>
       </c>
       <c r="J53" t="n">
-        <v>1169.17</v>
+        <v>342.17</v>
       </c>
       <c r="K53" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>3975.18</v>
+        <v>1368.68</v>
       </c>
       <c r="M53" t="n">
-        <v>559.8200000000001</v>
+        <v>350.09</v>
       </c>
       <c r="N53" t="n">
         <v>5</v>
@@ -3508,22 +3508,22 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ORD-000245</t>
+          <t>ORD-000053</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2023-01-22</t>
+          <t>2023-03-08</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>West</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Bihar</t>
+          <t>Gujarat</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3542,22 +3542,22 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="I54" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J54" t="n">
-        <v>3340.02</v>
+        <v>3178.12</v>
       </c>
       <c r="K54" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L54" t="n">
-        <v>3340.02</v>
+        <v>16208.41</v>
       </c>
       <c r="M54" t="n">
-        <v>1243</v>
+        <v>2764.16</v>
       </c>
       <c r="N54" t="n">
         <v>4</v>
@@ -3566,32 +3566,32 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ORD-000290</t>
+          <t>ORD-000054</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2023-01-22</t>
+          <t>2023-05-30</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>North</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Office Supplies</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Recycled Paper Ream</t>
+          <t>Wrinkle-Free Formal Shirt</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3600,36 +3600,36 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="I55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J55" t="n">
-        <v>462.35</v>
+        <v>2279.58</v>
       </c>
       <c r="K55" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="L55" t="n">
-        <v>462.35</v>
+        <v>3419.37</v>
       </c>
       <c r="M55" t="n">
-        <v>86.38</v>
+        <v>869.33</v>
       </c>
       <c r="N55" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ORD-000349</t>
+          <t>ORD-000055</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2023-01-22</t>
+          <t>2022-01-08</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3639,7 +3639,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Gujarat</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3649,7 +3649,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Steel Stapler Set</t>
+          <t>Executive Rollerball Pen</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3658,104 +3658,104 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="I56" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J56" t="n">
-        <v>578.21</v>
+        <v>840.96</v>
       </c>
       <c r="K56" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L56" t="n">
-        <v>2197.2</v>
+        <v>756.86</v>
       </c>
       <c r="M56" t="n">
-        <v>434.32</v>
+        <v>140.19</v>
       </c>
       <c r="N56" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ORD-000756</t>
+          <t>ORD-000056</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2023-01-22</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>East</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Telangana</t>
+          <t>West Bengal</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Fleece Hooded Sweatshirt</t>
+          <t>Laptop Pro</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Non-Binary</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="I57" t="n">
         <v>2</v>
       </c>
       <c r="J57" t="n">
-        <v>2907.16</v>
+        <v>66960.39999999999</v>
       </c>
       <c r="K57" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="L57" t="n">
-        <v>4942.17</v>
+        <v>133920.8</v>
       </c>
       <c r="M57" t="n">
-        <v>975.16</v>
+        <v>47937.7</v>
       </c>
       <c r="N57" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ORD-000388</t>
+          <t>ORD-000057</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2023-01-23</t>
+          <t>2022-11-02</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>North</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Assam</t>
+          <t>Punjab</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3765,7 +3765,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>LED Desk Lamp</t>
+          <t>Executive Leather Sofa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3774,36 +3774,36 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="I58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J58" t="n">
-        <v>2343.33</v>
+        <v>36201.74</v>
       </c>
       <c r="K58" t="n">
         <v>10</v>
       </c>
       <c r="L58" t="n">
-        <v>2109</v>
+        <v>65163.13</v>
       </c>
       <c r="M58" t="n">
-        <v>560.39</v>
+        <v>12562.33</v>
       </c>
       <c r="N58" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ORD-000598</t>
+          <t>ORD-000058</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2023-01-23</t>
+          <t>2022-03-27</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3813,17 +3813,17 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Rajasthan</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Wrinkle-Free Formal Shirt</t>
+          <t>Wireless Earbuds</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -3832,80 +3832,80 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="I59" t="n">
         <v>3</v>
       </c>
       <c r="J59" t="n">
-        <v>2296.33</v>
+        <v>4453.68</v>
       </c>
       <c r="K59" t="n">
         <v>10</v>
       </c>
       <c r="L59" t="n">
-        <v>6200.09</v>
+        <v>12024.94</v>
       </c>
       <c r="M59" t="n">
-        <v>986.79</v>
+        <v>1592.18</v>
       </c>
       <c r="N59" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ORD-000168</t>
+          <t>ORD-000059</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2023-01-24</t>
+          <t>2023-05-27</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>North</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Punjab</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Office Supplies</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Heavy-Duty Binder</t>
+          <t>Breathable Running Shoes</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Non-Binary</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="I60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J60" t="n">
-        <v>368.93</v>
+        <v>4386.15</v>
       </c>
       <c r="K60" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L60" t="n">
-        <v>700.97</v>
+        <v>4386.15</v>
       </c>
       <c r="M60" t="n">
-        <v>224.62</v>
+        <v>633.71</v>
       </c>
       <c r="N60" t="n">
         <v>4</v>
@@ -3914,32 +3914,32 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ORD-000528</t>
+          <t>ORD-000060</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2023-01-24</t>
+          <t>2022-11-13</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>South</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Odisha</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Furniture</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Slim-fit Denim Jeans</t>
+          <t>Executive Leather Sofa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -3948,104 +3948,104 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="I61" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J61" t="n">
-        <v>2772.07</v>
+        <v>32747.87</v>
       </c>
       <c r="K61" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L61" t="n">
-        <v>22176.56</v>
+        <v>62220.95</v>
       </c>
       <c r="M61" t="n">
-        <v>6725.41</v>
+        <v>15126.08</v>
       </c>
       <c r="N61" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ORD-000757</t>
+          <t>ORD-000061</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2023-01-24</t>
+          <t>2023-01-03</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>West</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Punjab</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Furniture</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Smart Fitness Watch</t>
+          <t>Modular Bookshelf</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Non-Binary</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="I62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J62" t="n">
-        <v>6115.17</v>
+        <v>7885.36</v>
       </c>
       <c r="K62" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L62" t="n">
-        <v>5503.65</v>
+        <v>12616.58</v>
       </c>
       <c r="M62" t="n">
-        <v>967.97</v>
+        <v>4422.58</v>
       </c>
       <c r="N62" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ORD-000325</t>
+          <t>ORD-000062</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2023-01-25</t>
+          <t>2022-08-10</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>East</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Punjab</t>
+          <t>West Bengal</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4055,55 +4055,55 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Breathable Running Shoes</t>
+          <t>Slim-fit Denim Jeans</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Non-Binary</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="I63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J63" t="n">
-        <v>4383.55</v>
+        <v>2801.41</v>
       </c>
       <c r="K63" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="L63" t="n">
-        <v>3506.84</v>
+        <v>4762.4</v>
       </c>
       <c r="M63" t="n">
-        <v>625.62</v>
+        <v>1387.1</v>
       </c>
       <c r="N63" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ORD-000695</t>
+          <t>ORD-000063</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2023-01-25</t>
+          <t>2024-07-31</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>West</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Assam</t>
+          <t>Rajasthan</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4113,7 +4113,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>LED Desk Lamp</t>
+          <t>Motorized Standing Desk</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -4122,36 +4122,36 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="I64" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J64" t="n">
-        <v>2091.28</v>
+        <v>25705.93</v>
       </c>
       <c r="K64" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="L64" t="n">
-        <v>19867.16</v>
+        <v>131100.24</v>
       </c>
       <c r="M64" t="n">
-        <v>4610.29</v>
+        <v>37424.52</v>
       </c>
       <c r="N64" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ORD-000045</t>
+          <t>ORD-000064</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2023-01-26</t>
+          <t>2023-01-31</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4161,133 +4161,133 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Bihar</t>
+          <t>Odisha</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Office Supplies</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Smart Fitness Watch</t>
+          <t>Recycled Paper Ream</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="I65" t="n">
         <v>1</v>
       </c>
       <c r="J65" t="n">
-        <v>5777.74</v>
+        <v>460.32</v>
       </c>
       <c r="K65" t="n">
         <v>5</v>
       </c>
       <c r="L65" t="n">
-        <v>5488.85</v>
+        <v>437.3</v>
       </c>
       <c r="M65" t="n">
-        <v>1190.52</v>
+        <v>114.51</v>
       </c>
       <c r="N65" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>ORD-000196</t>
+          <t>ORD-000065</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2023-01-26</t>
+          <t>2023-12-21</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>East</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Gujarat</t>
+          <t>Odisha</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Furniture</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>LED Desk Lamp</t>
+          <t>Laptop Pro</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="H66" t="n">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="I66" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J66" t="n">
-        <v>2243.27</v>
+        <v>66575.44</v>
       </c>
       <c r="K66" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L66" t="n">
-        <v>4037.89</v>
+        <v>266301.76</v>
       </c>
       <c r="M66" t="n">
-        <v>521.15</v>
+        <v>50924.86</v>
       </c>
       <c r="N66" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ORD-000592</t>
+          <t>ORD-000066</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2023-01-26</t>
+          <t>2023-01-01</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>West</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Assam</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Furniture</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ergonomic Mesh Chair</t>
+          <t>Smart Fitness Watch</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -4296,22 +4296,22 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="I67" t="n">
         <v>1</v>
       </c>
       <c r="J67" t="n">
-        <v>12329.94</v>
+        <v>5610.67</v>
       </c>
       <c r="K67" t="n">
         <v>10</v>
       </c>
       <c r="L67" t="n">
-        <v>11096.95</v>
+        <v>5049.6</v>
       </c>
       <c r="M67" t="n">
-        <v>2445.94</v>
+        <v>699.42</v>
       </c>
       <c r="N67" t="n">
         <v>4</v>
@@ -4320,22 +4320,22 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ORD-000904</t>
+          <t>ORD-000067</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2023-01-26</t>
+          <t>2023-12-09</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>West</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Odisha</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4354,46 +4354,46 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I68" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J68" t="n">
-        <v>29723.94</v>
+        <v>27286</v>
       </c>
       <c r="K68" t="n">
         <v>0</v>
       </c>
       <c r="L68" t="n">
-        <v>59447.88</v>
+        <v>81858</v>
       </c>
       <c r="M68" t="n">
-        <v>13381.89</v>
+        <v>20380.16</v>
       </c>
       <c r="N68" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ORD-000944</t>
+          <t>ORD-000068</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2023-01-26</t>
+          <t>2023-01-25</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>West</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Telangana</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4403,55 +4403,55 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Fleece Hooded Sweatshirt</t>
+          <t>Premium Cotton T-Shirt</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Non-Binary</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="I69" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J69" t="n">
-        <v>3086.22</v>
+        <v>1272.47</v>
       </c>
       <c r="K69" t="n">
         <v>10</v>
       </c>
       <c r="L69" t="n">
-        <v>11110.39</v>
+        <v>2290.45</v>
       </c>
       <c r="M69" t="n">
-        <v>2468.24</v>
+        <v>753.34</v>
       </c>
       <c r="N69" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ORD-000201</t>
+          <t>ORD-000069</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2023-01-27</t>
+          <t>2023-02-08</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>West</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4461,65 +4461,65 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Laptop Pro</t>
+          <t>Wireless Earbuds</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Non-Binary</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>62</v>
+        <v>27</v>
       </c>
       <c r="I70" t="n">
         <v>2</v>
       </c>
       <c r="J70" t="n">
-        <v>65961.03999999999</v>
+        <v>4549.33</v>
       </c>
       <c r="K70" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="L70" t="n">
-        <v>112133.77</v>
+        <v>8643.73</v>
       </c>
       <c r="M70" t="n">
-        <v>23596.35</v>
+        <v>2681.53</v>
       </c>
       <c r="N70" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ORD-000862</t>
+          <t>ORD-000070</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2023-01-27</t>
+          <t>2023-10-05</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>North</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>Punjab</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Furniture</t>
+          <t>Office Supplies</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Executive Leather Sofa</t>
+          <t>Steel Stapler Set</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -4528,104 +4528,104 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="I71" t="n">
+        <v>3</v>
+      </c>
+      <c r="J71" t="n">
+        <v>584.72</v>
+      </c>
+      <c r="K71" t="n">
+        <v>20</v>
+      </c>
+      <c r="L71" t="n">
+        <v>1403.33</v>
+      </c>
+      <c r="M71" t="n">
+        <v>481.61</v>
+      </c>
+      <c r="N71" t="n">
         <v>4</v>
-      </c>
-      <c r="J71" t="n">
-        <v>34339.89</v>
-      </c>
-      <c r="K71" t="n">
-        <v>0</v>
-      </c>
-      <c r="L71" t="n">
-        <v>137359.56</v>
-      </c>
-      <c r="M71" t="n">
-        <v>23507.57</v>
-      </c>
-      <c r="N71" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ORD-000954</t>
+          <t>ORD-000071</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2023-01-27</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>West</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Odisha</t>
+          <t>Gujarat</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Office Supplies</t>
+          <t>Furniture</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Steel Stapler Set</t>
+          <t>Executive Leather Sofa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Non-Binary</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="I72" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J72" t="n">
-        <v>634.89</v>
+        <v>33534.12</v>
       </c>
       <c r="K72" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L72" t="n">
-        <v>1269.78</v>
+        <v>95572.24000000001</v>
       </c>
       <c r="M72" t="n">
-        <v>340.29</v>
+        <v>24746.06</v>
       </c>
       <c r="N72" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ORD-000037</t>
+          <t>ORD-000072</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2023-01-28</t>
+          <t>2024-02-16</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>South</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Telangana</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4635,7 +4635,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Wrinkle-Free Formal Shirt</t>
+          <t>Breathable Running Shoes</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -4644,152 +4644,152 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="I73" t="n">
         <v>1</v>
       </c>
       <c r="J73" t="n">
-        <v>2354.93</v>
+        <v>4784.78</v>
       </c>
       <c r="K73" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="L73" t="n">
-        <v>1766.2</v>
+        <v>4545.54</v>
       </c>
       <c r="M73" t="n">
-        <v>342.32</v>
+        <v>558.27</v>
       </c>
       <c r="N73" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ORD-000811</t>
+          <t>ORD-000073</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2023-01-28</t>
+          <t>2023-09-15</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>West</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Assam</t>
+          <t>Gujarat</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Smart Fitness Watch</t>
+          <t>Breathable Running Shoes</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Non-Binary</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="I74" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J74" t="n">
-        <v>5897.81</v>
+        <v>4828.9</v>
       </c>
       <c r="K74" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L74" t="n">
-        <v>35386.86</v>
+        <v>4346.01</v>
       </c>
       <c r="M74" t="n">
-        <v>10426.54</v>
+        <v>1066.75</v>
       </c>
       <c r="N74" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ORD-000835</t>
+          <t>ORD-000074</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2023-01-28</t>
+          <t>2023-10-22</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>East</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Haryana</t>
+          <t>Assam</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Laptop Pro</t>
+          <t>Slim-fit Denim Jeans</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Non-Binary</t>
         </is>
       </c>
       <c r="H75" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="I75" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J75" t="n">
-        <v>63388.18</v>
+        <v>2707.36</v>
       </c>
       <c r="K75" t="n">
         <v>0</v>
       </c>
       <c r="L75" t="n">
-        <v>316940.9</v>
+        <v>5414.72</v>
       </c>
       <c r="M75" t="n">
-        <v>54863.4</v>
+        <v>1596.56</v>
       </c>
       <c r="N75" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ORD-000912</t>
+          <t>ORD-000075</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2023-01-28</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -4809,89 +4809,89 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Recycled Paper Ream</t>
+          <t>Magnetic Whiteboard</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Non-Binary</t>
         </is>
       </c>
       <c r="H76" t="n">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="I76" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J76" t="n">
-        <v>428.53</v>
+        <v>3002.09</v>
       </c>
       <c r="K76" t="n">
         <v>20</v>
       </c>
       <c r="L76" t="n">
-        <v>342.82</v>
+        <v>7205.02</v>
       </c>
       <c r="M76" t="n">
-        <v>108.92</v>
+        <v>2689.67</v>
       </c>
       <c r="N76" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ORD-000946</t>
+          <t>ORD-000076</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2023-01-28</t>
+          <t>2023-11-18</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>North</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Office Supplies</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Premium Cotton T-Shirt</t>
+          <t>Executive Rollerball Pen</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Non-Binary</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="H77" t="n">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="I77" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J77" t="n">
-        <v>1207.21</v>
+        <v>856.24</v>
       </c>
       <c r="K77" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L77" t="n">
-        <v>7243.26</v>
+        <v>2311.85</v>
       </c>
       <c r="M77" t="n">
-        <v>1354.38</v>
+        <v>859.66</v>
       </c>
       <c r="N77" t="n">
         <v>4</v>
@@ -4900,32 +4900,32 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ORD-000376</t>
+          <t>ORD-000077</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2023-01-29</t>
+          <t>2022-10-29</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>North</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Bihar</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Furniture</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Fleece Hooded Sweatshirt</t>
+          <t>Executive Leather Sofa</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -4934,46 +4934,46 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I78" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J78" t="n">
-        <v>3342.25</v>
+        <v>36895.49</v>
       </c>
       <c r="K78" t="n">
         <v>5</v>
       </c>
       <c r="L78" t="n">
-        <v>3175.14</v>
+        <v>140202.86</v>
       </c>
       <c r="M78" t="n">
-        <v>482.09</v>
+        <v>24937.86</v>
       </c>
       <c r="N78" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ORD-000389</t>
+          <t>ORD-000078</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2023-01-29</t>
+          <t>2022-05-30</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>East</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Telangana</t>
+          <t>Assam</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -4983,7 +4983,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>LED Desk Lamp</t>
+          <t>Executive Leather Sofa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -4992,36 +4992,36 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="I79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J79" t="n">
-        <v>2328.33</v>
+        <v>32655.55</v>
       </c>
       <c r="K79" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L79" t="n">
-        <v>4423.83</v>
+        <v>97966.64999999999</v>
       </c>
       <c r="M79" t="n">
-        <v>968.39</v>
+        <v>36887.02</v>
       </c>
       <c r="N79" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ORD-000704</t>
+          <t>ORD-000079</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2023-01-29</t>
+          <t>2024-03-29</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5031,55 +5031,55 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Telangana</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Furniture</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Modular Bookshelf</t>
+          <t>Laptop Pro</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Non-Binary</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="H80" t="n">
-        <v>63</v>
+        <v>18</v>
       </c>
       <c r="I80" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J80" t="n">
-        <v>7946.75</v>
+        <v>62261.53</v>
       </c>
       <c r="K80" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="L80" t="n">
-        <v>7549.41</v>
+        <v>249046.12</v>
       </c>
       <c r="M80" t="n">
-        <v>1226.53</v>
+        <v>68211.50999999999</v>
       </c>
       <c r="N80" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ORD-000767</t>
+          <t>ORD-000080</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2023-01-29</t>
+          <t>2023-03-25</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5089,41 +5089,41 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Telangana</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Furniture</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>LED Desk Lamp</t>
+          <t>Smart Fitness Watch</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="H81" t="n">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I81" t="n">
         <v>2</v>
       </c>
       <c r="J81" t="n">
-        <v>2341.65</v>
+        <v>5882.87</v>
       </c>
       <c r="K81" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L81" t="n">
-        <v>4449.13</v>
+        <v>10589.17</v>
       </c>
       <c r="M81" t="n">
-        <v>784.14</v>
+        <v>1955.48</v>
       </c>
       <c r="N81" t="n">
         <v>4</v>
@@ -5132,90 +5132,90 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ORD-000856</t>
+          <t>ORD-000081</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2023-01-29</t>
+          <t>2022-09-06</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>East</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Bihar</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Smart Fitness Watch</t>
+          <t>Breathable Running Shoes</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Non-Binary</t>
         </is>
       </c>
       <c r="H82" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="I82" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J82" t="n">
-        <v>5731.69</v>
+        <v>4431.75</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L82" t="n">
-        <v>17195.07</v>
+        <v>4210.16</v>
       </c>
       <c r="M82" t="n">
-        <v>6314.25</v>
+        <v>1316.32</v>
       </c>
       <c r="N82" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ORD-000980</t>
+          <t>ORD-000082</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2023-01-29</t>
+          <t>2023-10-12</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>East</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Rajasthan</t>
+          <t>Assam</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Smartphone 5G</t>
+          <t>Slim-fit Denim Jeans</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -5224,22 +5224,22 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="I83" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J83" t="n">
-        <v>29968.47</v>
+        <v>2881.11</v>
       </c>
       <c r="K83" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L83" t="n">
-        <v>28470.05</v>
+        <v>8643.33</v>
       </c>
       <c r="M83" t="n">
-        <v>7032.7</v>
+        <v>1936.61</v>
       </c>
       <c r="N83" t="n">
         <v>4</v>
@@ -5248,12 +5248,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>ORD-000377</t>
+          <t>ORD-000083</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2023-01-30</t>
+          <t>2024-08-30</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5268,70 +5268,70 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Furniture</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ultra-wide Monitor</t>
+          <t>Modular Bookshelf</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Non-Binary</t>
         </is>
       </c>
       <c r="H84" t="n">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="I84" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J84" t="n">
-        <v>29711.04</v>
+        <v>8124.09</v>
       </c>
       <c r="K84" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="L84" t="n">
-        <v>28225.49</v>
+        <v>25997.09</v>
       </c>
       <c r="M84" t="n">
-        <v>4577.63</v>
+        <v>3201.81</v>
       </c>
       <c r="N84" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>ORD-000633</t>
+          <t>ORD-000084</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2023-01-30</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>South</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Odisha</t>
+          <t>Telangana</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Furniture</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ergonomic Mesh Chair</t>
+          <t>Premium Cotton T-Shirt</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -5340,22 +5340,22 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="I85" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J85" t="n">
-        <v>11890.33</v>
+        <v>1205.32</v>
       </c>
       <c r="K85" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="L85" t="n">
-        <v>11295.81</v>
+        <v>4519.95</v>
       </c>
       <c r="M85" t="n">
-        <v>3533.63</v>
+        <v>629.12</v>
       </c>
       <c r="N85" t="n">
         <v>4</v>
@@ -5364,70 +5364,70 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ORD-000882</t>
+          <t>ORD-000085</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2023-01-30</t>
+          <t>2023-08-09</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>South</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Telangana</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Office Supplies</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Wireless Earbuds</t>
+          <t>Heavy-Duty Binder</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Non-Binary</t>
         </is>
       </c>
       <c r="H86" t="n">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="I86" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J86" t="n">
-        <v>4314.49</v>
+        <v>331.31</v>
       </c>
       <c r="K86" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L86" t="n">
-        <v>31064.33</v>
+        <v>331.31</v>
       </c>
       <c r="M86" t="n">
-        <v>10504.9</v>
+        <v>65.13</v>
       </c>
       <c r="N86" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ORD-000042</t>
+          <t>ORD-000086</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2023-01-31</t>
+          <t>2022-06-15</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -5437,55 +5437,55 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Furniture</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ultra-wide Monitor</t>
+          <t>Executive Leather Sofa</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Non-Binary</t>
         </is>
       </c>
       <c r="H87" t="n">
-        <v>64</v>
+        <v>20</v>
       </c>
       <c r="I87" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J87" t="n">
-        <v>26634.69</v>
+        <v>32454.5</v>
       </c>
       <c r="K87" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L87" t="n">
-        <v>47942.44</v>
+        <v>162272.5</v>
       </c>
       <c r="M87" t="n">
-        <v>9252.93</v>
+        <v>59571.37</v>
       </c>
       <c r="N87" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ORD-000316</t>
+          <t>ORD-000087</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2023-01-31</t>
+          <t>2022-11-09</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -5495,7 +5495,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5514,46 +5514,46 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="I88" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J88" t="n">
-        <v>3156.51</v>
+        <v>3018.49</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
       </c>
       <c r="L88" t="n">
-        <v>6313.02</v>
+        <v>3018.49</v>
       </c>
       <c r="M88" t="n">
-        <v>1608.47</v>
+        <v>869.87</v>
       </c>
       <c r="N88" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>ORD-000487</t>
+          <t>ORD-000088</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2023-01-31</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>East</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Gujarat</t>
+          <t>West Bengal</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5563,45 +5563,45 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Motorized Standing Desk</t>
+          <t>Executive Leather Sofa</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="H89" t="n">
-        <v>25</v>
+        <v>67</v>
       </c>
       <c r="I89" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J89" t="n">
-        <v>23570.56</v>
+        <v>34217.93</v>
       </c>
       <c r="K89" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L89" t="n">
-        <v>42427.01</v>
+        <v>34217.93</v>
       </c>
       <c r="M89" t="n">
-        <v>7958.26</v>
+        <v>8138.48</v>
       </c>
       <c r="N89" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>ORD-000515</t>
+          <t>ORD-000089</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2023-01-31</t>
+          <t>2022-02-10</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -5611,65 +5611,65 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Odisha</t>
+          <t>Assam</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Fleece Hooded Sweatshirt</t>
+          <t>Wireless Earbuds</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Non-Binary</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="H90" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="I90" t="n">
         <v>1</v>
       </c>
       <c r="J90" t="n">
-        <v>3334.65</v>
+        <v>4725.93</v>
       </c>
       <c r="K90" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L90" t="n">
-        <v>3334.65</v>
+        <v>4253.34</v>
       </c>
       <c r="M90" t="n">
-        <v>663.9</v>
+        <v>690.23</v>
       </c>
       <c r="N90" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ORD-000674</t>
+          <t>ORD-000090</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2023-01-31</t>
+          <t>2024-03-09</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>East</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>Bihar</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -5679,7 +5679,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Breathable Running Shoes</t>
+          <t>Slim-fit Denim Jeans</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -5688,36 +5688,36 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="I91" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J91" t="n">
-        <v>4638.25</v>
+        <v>2901.12</v>
       </c>
       <c r="K91" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L91" t="n">
-        <v>4406.34</v>
+        <v>15666.05</v>
       </c>
       <c r="M91" t="n">
-        <v>788.27</v>
+        <v>3583.5</v>
       </c>
       <c r="N91" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ORD-000542</t>
+          <t>ORD-000091</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2023-02-01</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -5727,75 +5727,75 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Bihar</t>
+          <t>West Bengal</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Furniture</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Modular Bookshelf</t>
+          <t>Wrinkle-Free Formal Shirt</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Non-Binary</t>
         </is>
       </c>
       <c r="H92" t="n">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="I92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J92" t="n">
-        <v>8405.309999999999</v>
+        <v>2082.02</v>
       </c>
       <c r="K92" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L92" t="n">
-        <v>7564.78</v>
+        <v>3955.84</v>
       </c>
       <c r="M92" t="n">
-        <v>1808.63</v>
+        <v>1274.48</v>
       </c>
       <c r="N92" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ORD-000273</t>
+          <t>ORD-000092</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2023-02-02</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>South</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Haryana</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Furniture</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Smart Fitness Watch</t>
+          <t>LED Desk Lamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -5804,36 +5804,36 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="I93" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J93" t="n">
-        <v>5603.56</v>
+        <v>2233.13</v>
       </c>
       <c r="K93" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="L93" t="n">
-        <v>9526.049999999999</v>
+        <v>2121.47</v>
       </c>
       <c r="M93" t="n">
-        <v>2068.22</v>
+        <v>789.5599999999999</v>
       </c>
       <c r="N93" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ORD-000281</t>
+          <t>ORD-000093</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2023-02-02</t>
+          <t>2022-02-25</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -5848,12 +5848,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Office Supplies</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Executive Rollerball Pen</t>
+          <t>Ultra-wide Monitor</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -5862,104 +5862,104 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="I94" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J94" t="n">
-        <v>784.15</v>
+        <v>25924.96</v>
       </c>
       <c r="K94" t="n">
         <v>0</v>
       </c>
       <c r="L94" t="n">
-        <v>2352.45</v>
+        <v>25924.96</v>
       </c>
       <c r="M94" t="n">
-        <v>783.05</v>
+        <v>3203.15</v>
       </c>
       <c r="N94" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ORD-000875</t>
+          <t>ORD-000094</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2023-02-02</t>
+          <t>2024-08-03</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>South</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Bihar</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Office Supplies</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Breathable Running Shoes</t>
+          <t>Steel Stapler Set</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="H95" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="I95" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J95" t="n">
-        <v>4739.71</v>
+        <v>647.97</v>
       </c>
       <c r="K95" t="n">
         <v>25</v>
       </c>
       <c r="L95" t="n">
-        <v>10664.35</v>
+        <v>1943.91</v>
       </c>
       <c r="M95" t="n">
-        <v>3473.74</v>
+        <v>513.99</v>
       </c>
       <c r="N95" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ORD-000206</t>
+          <t>ORD-000095</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2023-02-03</t>
+          <t>2023-03-10</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>East</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Telangana</t>
+          <t>Odisha</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -5974,108 +5974,108 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Non-Binary</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="H96" t="n">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="I96" t="n">
         <v>3</v>
       </c>
       <c r="J96" t="n">
-        <v>576.83</v>
+        <v>588.27</v>
       </c>
       <c r="K96" t="n">
         <v>0</v>
       </c>
       <c r="L96" t="n">
-        <v>1730.49</v>
+        <v>1764.81</v>
       </c>
       <c r="M96" t="n">
-        <v>245.5</v>
+        <v>305.86</v>
       </c>
       <c r="N96" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ORD-000554</t>
+          <t>ORD-000096</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2023-02-03</t>
+          <t>2024-05-13</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>West</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Furniture</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Ergonomic Mesh Chair</t>
+          <t>Premium Cotton T-Shirt</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Non-Binary</t>
         </is>
       </c>
       <c r="H97" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="I97" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J97" t="n">
-        <v>11662.3</v>
+        <v>1147.9</v>
       </c>
       <c r="K97" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="L97" t="n">
-        <v>27989.52</v>
+        <v>2066.22</v>
       </c>
       <c r="M97" t="n">
-        <v>9460.68</v>
+        <v>580.02</v>
       </c>
       <c r="N97" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ORD-000033</t>
+          <t>ORD-000097</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2023-02-04</t>
+          <t>2022-04-17</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>West</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Punjab</t>
+          <t>Gujarat</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -6085,7 +6085,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Smart Fitness Watch</t>
+          <t>Laptop Pro</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -6094,114 +6094,114 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>67</v>
+        <v>25</v>
       </c>
       <c r="I98" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J98" t="n">
-        <v>6362.25</v>
+        <v>64980.92</v>
       </c>
       <c r="K98" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L98" t="n">
-        <v>31811.25</v>
+        <v>61731.87</v>
       </c>
       <c r="M98" t="n">
-        <v>9276.030000000001</v>
+        <v>20751.57</v>
       </c>
       <c r="N98" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ORD-000278</t>
+          <t>ORD-000098</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2023-02-04</t>
+          <t>2023-05-22</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>South</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Gujarat</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Furniture</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Smart Fitness Watch</t>
+          <t>Motorized Standing Desk</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Non-Binary</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="H99" t="n">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="I99" t="n">
+        <v>2</v>
+      </c>
+      <c r="J99" t="n">
+        <v>24234</v>
+      </c>
+      <c r="K99" t="n">
+        <v>15</v>
+      </c>
+      <c r="L99" t="n">
+        <v>41197.8</v>
+      </c>
+      <c r="M99" t="n">
+        <v>9265.610000000001</v>
+      </c>
+      <c r="N99" t="n">
         <v>3</v>
-      </c>
-      <c r="J99" t="n">
-        <v>6348.29</v>
-      </c>
-      <c r="K99" t="n">
-        <v>0</v>
-      </c>
-      <c r="L99" t="n">
-        <v>19044.87</v>
-      </c>
-      <c r="M99" t="n">
-        <v>2759.33</v>
-      </c>
-      <c r="N99" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>ORD-000460</t>
+          <t>ORD-000099</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2023-02-04</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>North</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Laptop Pro</t>
+          <t>Wrinkle-Free Formal Shirt</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -6210,83 +6210,83 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>29</v>
+        <v>64</v>
       </c>
       <c r="I100" t="n">
         <v>2</v>
       </c>
       <c r="J100" t="n">
-        <v>62756.45</v>
+        <v>2300.2</v>
       </c>
       <c r="K100" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L100" t="n">
-        <v>125512.9</v>
+        <v>4140.36</v>
       </c>
       <c r="M100" t="n">
-        <v>35606.13</v>
+        <v>1363.47</v>
       </c>
       <c r="N100" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>ORD-000717</t>
+          <t>ORD-000100</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2023-02-04</t>
+          <t>2022-12-10</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>North</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Office Supplies</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Premium Cotton T-Shirt</t>
+          <t>Recycled Paper Ream</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Non-Binary</t>
         </is>
       </c>
       <c r="H101" t="n">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="I101" t="n">
         <v>1</v>
       </c>
       <c r="J101" t="n">
-        <v>1123.11</v>
+        <v>456.47</v>
       </c>
       <c r="K101" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L101" t="n">
-        <v>1010.8</v>
+        <v>433.65</v>
       </c>
       <c r="M101" t="n">
-        <v>258.9</v>
+        <v>101.36</v>
       </c>
       <c r="N101" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6378,12 +6378,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ORD-000583</t>
+          <t>ORD-000001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2023-01-01</t>
+          <t>2022-08-17</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -6393,17 +6393,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Haryana</t>
+          <t>Punjab</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Furniture</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fleece Hooded Sweatshirt</t>
+          <t>Motorized Standing Desk</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6412,94 +6412,94 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J2" t="n">
-        <v>3089.71</v>
+        <v>22784.39</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L2" t="n">
-        <v>3089.71</v>
+        <v>61517.85</v>
       </c>
       <c r="M2" t="n">
-        <v>967.7</v>
+        <v>16928.55</v>
       </c>
       <c r="N2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ORD-000057</t>
+          <t>ORD-000002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2023-01-02</t>
+          <t>2022-07-29</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>North</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Gujarat</t>
+          <t>Haryana</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Office Supplies</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Executive Rollerball Pen</t>
+          <t>Laptop Pro</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Non-Binary</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>879.1900000000001</v>
+        <v>68808.23</v>
       </c>
       <c r="K3" t="n">
         <v>10</v>
       </c>
       <c r="L3" t="n">
-        <v>1582.54</v>
+        <v>61927.41</v>
       </c>
       <c r="M3" t="n">
-        <v>305.09</v>
+        <v>18832.06</v>
       </c>
       <c r="N3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ORD-000378</t>
+          <t>ORD-000003</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2023-01-02</t>
+          <t>2023-03-24</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -6514,12 +6514,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Furniture</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ultra-wide Monitor</t>
+          <t>LED Desk Lamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -6528,22 +6528,22 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J4" t="n">
-        <v>25891.55</v>
+        <v>2354.37</v>
       </c>
       <c r="K4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>22007.82</v>
+        <v>7063.11</v>
       </c>
       <c r="M4" t="n">
-        <v>3841.15</v>
+        <v>2669.68</v>
       </c>
       <c r="N4" t="n">
         <v>4</v>
@@ -6552,12 +6552,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ORD-000593</t>
+          <t>ORD-000004</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2023-01-02</t>
+          <t>2023-03-28</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -6567,55 +6567,55 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>West Bengal</t>
+          <t>Odisha</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Office Supplies</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Magnetic Whiteboard</t>
+          <t>Smartphone 5G</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Non-Binary</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>29558.08</v>
+      </c>
+      <c r="K5" t="n">
+        <v>5</v>
+      </c>
+      <c r="L5" t="n">
+        <v>28080.18</v>
+      </c>
+      <c r="M5" t="n">
+        <v>6288.95</v>
+      </c>
+      <c r="N5" t="n">
         <v>2</v>
-      </c>
-      <c r="J5" t="n">
-        <v>3385.1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>15</v>
-      </c>
-      <c r="L5" t="n">
-        <v>5754.67</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1774.33</v>
-      </c>
-      <c r="N5" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ORD-000714</t>
+          <t>ORD-000005</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2023-01-03</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -6625,7 +6625,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Rajasthan</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -6635,103 +6635,103 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ergonomic Mesh Chair</t>
+          <t>Motorized Standing Desk</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="I6" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>13454.56</v>
+        <v>22427.93</v>
       </c>
       <c r="K6" t="n">
         <v>10</v>
       </c>
       <c r="L6" t="n">
-        <v>96872.83</v>
+        <v>20185.14</v>
       </c>
       <c r="M6" t="n">
-        <v>28233.58</v>
+        <v>4429.43</v>
       </c>
       <c r="N6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ORD-000736</t>
+          <t>ORD-000006</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2023-01-03</t>
+          <t>2022-07-29</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>North</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>West Bengal</t>
+          <t>Haryana</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Office Supplies</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Executive Rollerball Pen</t>
+          <t>Wireless Earbuds</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Non-Binary</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J7" t="n">
-        <v>851.97</v>
+        <v>4629.82</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L7" t="n">
-        <v>1703.94</v>
+        <v>17593.32</v>
       </c>
       <c r="M7" t="n">
-        <v>447.64</v>
+        <v>2171.88</v>
       </c>
       <c r="N7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ORD-000779</t>
+          <t>ORD-000007</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2023-01-03</t>
+          <t>2023-06-26</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -6741,7 +6741,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Haryana</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -6756,108 +6756,108 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Non-Binary</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J8" t="n">
-        <v>29024.96</v>
+        <v>27124.67</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>87074.88</v>
+        <v>108498.68</v>
       </c>
       <c r="M8" t="n">
-        <v>31459.58</v>
+        <v>32321.82</v>
       </c>
       <c r="N8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ORD-000005</t>
+          <t>ORD-000008</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2023-01-04</t>
+          <t>2023-08-24</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>West</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Gujarat</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Office Supplies</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Heavy-Duty Binder</t>
+          <t>Laptop Pro</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Non-Binary</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J9" t="n">
-        <v>327.07</v>
+        <v>68465.23</v>
       </c>
       <c r="K9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>294.36</v>
+        <v>136930.46</v>
       </c>
       <c r="M9" t="n">
-        <v>64.59</v>
+        <v>30354.16</v>
       </c>
       <c r="N9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ORD-000761</t>
+          <t>ORD-000009</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2023-01-04</t>
+          <t>2023-04-12</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>West</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -6867,147 +6867,147 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Motorized Standing Desk</t>
+          <t>Ergonomic Mesh Chair</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>65</v>
+        <v>21</v>
       </c>
       <c r="I10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>25261.2</v>
+        <v>12540.14</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L10" t="n">
-        <v>50522.4</v>
+        <v>11913.13</v>
       </c>
       <c r="M10" t="n">
-        <v>12326.36</v>
+        <v>2002.15</v>
       </c>
       <c r="N10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ORD-000177</t>
+          <t>ORD-000010</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2023-01-05</t>
+          <t>2023-07-24</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>East</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Haryana</t>
+          <t>Odisha</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Office Supplies</t>
+          <t>Furniture</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Executive Rollerball Pen</t>
+          <t>Modular Bookshelf</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Non-Binary</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="I11" t="n">
         <v>2</v>
       </c>
       <c r="J11" t="n">
-        <v>885.23</v>
+        <v>8357.4</v>
       </c>
       <c r="K11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L11" t="n">
-        <v>1593.41</v>
+        <v>13371.84</v>
       </c>
       <c r="M11" t="n">
-        <v>455.21</v>
+        <v>4133.11</v>
       </c>
       <c r="N11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ORD-000627</t>
+          <t>ORD-000011</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2023-01-05</t>
+          <t>2023-03-06</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>West</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Telangana</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Office Supplies</t>
+          <t>Furniture</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Heavy-Duty Binder</t>
+          <t>LED Desk Lamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Non-Binary</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="I12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>365.5</v>
+        <v>2039.92</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1827.5</v>
+        <v>2039.92</v>
       </c>
       <c r="M12" t="n">
-        <v>688.14</v>
+        <v>450.94</v>
       </c>
       <c r="N12" t="n">
         <v>3</v>
@@ -7016,56 +7016,56 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ORD-000844</t>
+          <t>ORD-000012</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2023-01-05</t>
+          <t>2023-05-17</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>South</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Assam</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Office Supplies</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Recycled Paper Ream</t>
+          <t>Wrinkle-Free Formal Shirt</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Non-Binary</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>414.5</v>
+        <v>2122.89</v>
       </c>
       <c r="K13" t="n">
         <v>5</v>
       </c>
       <c r="L13" t="n">
-        <v>393.77</v>
+        <v>2016.75</v>
       </c>
       <c r="M13" t="n">
-        <v>71.29000000000001</v>
+        <v>315.9</v>
       </c>
       <c r="N13" t="n">
         <v>5</v>
@@ -7074,22 +7074,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ORD-000864</t>
+          <t>ORD-000013</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2023-01-05</t>
+          <t>2023-03-26</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>West</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Haryana</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -7099,55 +7099,55 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Modular Bookshelf</t>
+          <t>Ergonomic Mesh Chair</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>8457.9</v>
+        <v>12346.8</v>
       </c>
       <c r="K14" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="L14" t="n">
-        <v>7189.22</v>
+        <v>11729.46</v>
       </c>
       <c r="M14" t="n">
-        <v>1199.46</v>
+        <v>2302.57</v>
       </c>
       <c r="N14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ORD-000454</t>
+          <t>ORD-000014</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2023-01-06</t>
+          <t>2024-04-01</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>West</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Punjab</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -7166,22 +7166,22 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J15" t="n">
-        <v>2165.81</v>
+        <v>2302.14</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L15" t="n">
-        <v>2165.81</v>
+        <v>6215.78</v>
       </c>
       <c r="M15" t="n">
-        <v>390.76</v>
+        <v>2242.89</v>
       </c>
       <c r="N15" t="n">
         <v>4</v>
@@ -7190,12 +7190,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ORD-000791</t>
+          <t>ORD-000015</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2023-01-06</t>
+          <t>2023-10-07</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -7205,41 +7205,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Telangana</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Furniture</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ergonomic Mesh Chair</t>
+          <t>Fleece Hooded Sweatshirt</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Non-Binary</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J16" t="n">
-        <v>12105.66</v>
+        <v>3161.16</v>
       </c>
       <c r="K16" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>10895.09</v>
+        <v>12644.64</v>
       </c>
       <c r="M16" t="n">
-        <v>3292.37</v>
+        <v>1726.31</v>
       </c>
       <c r="N16" t="n">
         <v>4</v>
@@ -7248,12 +7248,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ORD-000863</t>
+          <t>ORD-000016</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2023-01-08</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -7263,99 +7263,99 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Telangana</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Office Supplies</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ultra-wide Monitor</t>
+          <t>Magnetic Whiteboard</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J17" t="n">
-        <v>29939.65</v>
+        <v>3246.74</v>
       </c>
       <c r="K17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>56885.33</v>
+        <v>9740.219999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>14607.1</v>
+        <v>2590.15</v>
       </c>
       <c r="N17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ORD-000514</t>
+          <t>ORD-000017</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2023-01-09</t>
+          <t>2024-03-28</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>West</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Gujarat</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Office Supplies</t>
+          <t>Furniture</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Executive Rollerball Pen</t>
+          <t>LED Desk Lamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J18" t="n">
-        <v>799.39</v>
+        <v>2291.8</v>
       </c>
       <c r="K18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L18" t="n">
-        <v>719.45</v>
+        <v>6531.63</v>
       </c>
       <c r="M18" t="n">
-        <v>86.34</v>
+        <v>2093.07</v>
       </c>
       <c r="N18" t="n">
         <v>4</v>
@@ -7364,12 +7364,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ORD-000099</t>
+          <t>ORD-000018</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2023-01-10</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Punjab</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -7389,7 +7389,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ergonomic Mesh Chair</t>
+          <t>Motorized Standing Desk</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -7398,22 +7398,22 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>64</v>
+        <v>26</v>
       </c>
       <c r="I19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J19" t="n">
-        <v>13069.34</v>
+        <v>22505.82</v>
       </c>
       <c r="K19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L19" t="n">
-        <v>23524.81</v>
+        <v>64141.59</v>
       </c>
       <c r="M19" t="n">
-        <v>7746.99</v>
+        <v>11061.02</v>
       </c>
       <c r="N19" t="n">
         <v>5</v>
@@ -7422,128 +7422,128 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ORD-000571</t>
+          <t>ORD-000019</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2023-01-11</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>North</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>West Bengal</t>
+          <t>Haryana</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Office Supplies</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Magnetic Whiteboard</t>
+          <t>Breathable Running Shoes</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="I20" t="n">
         <v>1</v>
       </c>
       <c r="J20" t="n">
-        <v>3156.07</v>
+        <v>4506.17</v>
       </c>
       <c r="K20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L20" t="n">
-        <v>2840.46</v>
+        <v>3604.94</v>
       </c>
       <c r="M20" t="n">
-        <v>991.98</v>
+        <v>666.25</v>
       </c>
       <c r="N20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ORD-000626</t>
+          <t>ORD-000020</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2023-01-11</t>
+          <t>2024-12-19</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>West</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Haryana</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Furniture</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Motorized Standing Desk</t>
+          <t>Smart Fitness Watch</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Non-Binary</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="I21" t="n">
         <v>1</v>
       </c>
       <c r="J21" t="n">
-        <v>23444.43</v>
+        <v>6425.14</v>
       </c>
       <c r="K21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L21" t="n">
-        <v>21099.99</v>
+        <v>6103.88</v>
       </c>
       <c r="M21" t="n">
-        <v>2875.23</v>
+        <v>1835.1</v>
       </c>
       <c r="N21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ORD-000657</t>
+          <t>ORD-000021</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2023-01-11</t>
+          <t>2023-11-28</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -7553,7 +7553,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Punjab</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -7563,7 +7563,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fleece Hooded Sweatshirt</t>
+          <t>Slim-fit Denim Jeans</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -7572,22 +7572,22 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="I22" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J22" t="n">
-        <v>3024.06</v>
+        <v>2859.76</v>
       </c>
       <c r="K22" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="L22" t="n">
-        <v>5745.71</v>
+        <v>9723.18</v>
       </c>
       <c r="M22" t="n">
-        <v>1876.35</v>
+        <v>3198.49</v>
       </c>
       <c r="N22" t="n">
         <v>3</v>
@@ -7596,56 +7596,56 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ORD-000852</t>
+          <t>ORD-000022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2023-01-12</t>
+          <t>2022-01-07</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>West</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>Gujarat</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Office Supplies</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Heavy-Duty Binder</t>
+          <t>Wireless Earbuds</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Non-Binary</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J23" t="n">
-        <v>368.84</v>
+        <v>4373.53</v>
       </c>
       <c r="K23" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>350.4</v>
+        <v>21867.65</v>
       </c>
       <c r="M23" t="n">
-        <v>43.36</v>
+        <v>4649.88</v>
       </c>
       <c r="N23" t="n">
         <v>5</v>
@@ -7654,12 +7654,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ORD-000063</t>
+          <t>ORD-000023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2023-01-13</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -7669,75 +7669,75 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Telangana</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Office Supplies</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Slim-fit Denim Jeans</t>
+          <t>Executive Rollerball Pen</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Non-Binary</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="I24" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
-        <v>2999.02</v>
+        <v>840.09</v>
       </c>
       <c r="K24" t="n">
         <v>15</v>
       </c>
       <c r="L24" t="n">
-        <v>15295</v>
+        <v>714.08</v>
       </c>
       <c r="M24" t="n">
-        <v>4366.19</v>
+        <v>245.49</v>
       </c>
       <c r="N24" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ORD-000066</t>
+          <t>ORD-000024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2023-01-13</t>
+          <t>2024-12-22</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>North</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Punjab</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Office Supplies</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Heavy-Duty Binder</t>
+          <t>Premium Cotton T-Shirt</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -7746,46 +7746,46 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J25" t="n">
-        <v>327.29</v>
+        <v>1197.09</v>
       </c>
       <c r="K25" t="n">
         <v>10</v>
       </c>
       <c r="L25" t="n">
-        <v>294.56</v>
+        <v>2154.76</v>
       </c>
       <c r="M25" t="n">
-        <v>40.8</v>
+        <v>409.51</v>
       </c>
       <c r="N25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ORD-000536</t>
+          <t>ORD-000025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2023-01-13</t>
+          <t>2024-01-14</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>West</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Telangana</t>
+          <t>Gujarat</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -7795,65 +7795,65 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Wireless Earbuds</t>
+          <t>Smartphone 5G</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Non-Binary</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J26" t="n">
-        <v>4847.08</v>
+        <v>33039.46</v>
       </c>
       <c r="K26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L26" t="n">
-        <v>4362.37</v>
+        <v>62774.97</v>
       </c>
       <c r="M26" t="n">
-        <v>1355.42</v>
+        <v>23393.93</v>
       </c>
       <c r="N26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ORD-000104</t>
+          <t>ORD-000026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2023-01-14</t>
+          <t>2022-06-11</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>North</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Haryana</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Slim-fit Denim Jeans</t>
+          <t>Smart Fitness Watch</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -7862,22 +7862,22 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J27" t="n">
-        <v>2633.36</v>
+        <v>5808.84</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>2633.36</v>
+        <v>11617.68</v>
       </c>
       <c r="M27" t="n">
-        <v>411.05</v>
+        <v>1505.54</v>
       </c>
       <c r="N27" t="n">
         <v>4</v>
@@ -7886,56 +7886,56 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ORD-000303</t>
+          <t>ORD-000027</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2023-01-14</t>
+          <t>2022-09-20</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>East</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Rajasthan</t>
+          <t>Bihar</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Office Supplies</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Breathable Running Shoes</t>
+          <t>Magnetic Whiteboard</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Non-Binary</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J28" t="n">
-        <v>4292.46</v>
+        <v>2960.92</v>
       </c>
       <c r="K28" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>4077.84</v>
+        <v>5921.84</v>
       </c>
       <c r="M28" t="n">
-        <v>1289.03</v>
+        <v>1687.32</v>
       </c>
       <c r="N28" t="n">
         <v>4</v>
@@ -7944,12 +7944,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ORD-000150</t>
+          <t>ORD-000028</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2023-01-15</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -7969,65 +7969,65 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Magnetic Whiteboard</t>
+          <t>Steel Stapler Set</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Non-Binary</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J29" t="n">
-        <v>3327.98</v>
+        <v>605.08</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L29" t="n">
-        <v>3327.98</v>
+        <v>1149.65</v>
       </c>
       <c r="M29" t="n">
-        <v>1176.42</v>
+        <v>162.13</v>
       </c>
       <c r="N29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ORD-000268</t>
+          <t>ORD-000029</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2023-01-15</t>
+          <t>2024-02-04</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>East</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Assam</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Office Supplies</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Executive Rollerball Pen</t>
+          <t>Smartphone 5G</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -8036,46 +8036,46 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>64</v>
+        <v>34</v>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J30" t="n">
-        <v>911.83</v>
+        <v>31323.05</v>
       </c>
       <c r="K30" t="n">
         <v>10</v>
       </c>
       <c r="L30" t="n">
-        <v>820.65</v>
+        <v>84572.24000000001</v>
       </c>
       <c r="M30" t="n">
-        <v>179.57</v>
+        <v>24079.22</v>
       </c>
       <c r="N30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ORD-000624</t>
+          <t>ORD-000030</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2023-01-15</t>
+          <t>2022-05-12</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>West</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>West Bengal</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -8094,22 +8094,22 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J31" t="n">
-        <v>2075.84</v>
+        <v>2077.05</v>
       </c>
       <c r="K31" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="L31" t="n">
-        <v>1556.88</v>
+        <v>5919.59</v>
       </c>
       <c r="M31" t="n">
-        <v>494.18</v>
+        <v>1781.27</v>
       </c>
       <c r="N31" t="n">
         <v>5</v>
